--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35181-2026 artfynd.xlsx
+++ b/artfynd/A 35181-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855662</v>
       </c>
       <c r="B2" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
